--- a/artfynd/A 15895-2026 artfynd.xlsx
+++ b/artfynd/A 15895-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132080747</v>
       </c>
       <c r="B2" t="n">
-        <v>97915</v>
+        <v>97920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132080746</v>
       </c>
       <c r="B3" t="n">
-        <v>97912</v>
+        <v>97917</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15895-2026 artfynd.xlsx
+++ b/artfynd/A 15895-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132080747</v>
       </c>
       <c r="B2" t="n">
-        <v>97920</v>
+        <v>97922</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132080746</v>
       </c>
       <c r="B3" t="n">
-        <v>97917</v>
+        <v>97919</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15895-2026 artfynd.xlsx
+++ b/artfynd/A 15895-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132080747</v>
       </c>
       <c r="B2" t="n">
-        <v>97922</v>
+        <v>97958</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132080746</v>
       </c>
       <c r="B3" t="n">
-        <v>97919</v>
+        <v>97955</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15895-2026 artfynd.xlsx
+++ b/artfynd/A 15895-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132080747</v>
       </c>
       <c r="B2" t="n">
-        <v>97963</v>
+        <v>97966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132080746</v>
       </c>
       <c r="B3" t="n">
-        <v>97960</v>
+        <v>97963</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15895-2026 artfynd.xlsx
+++ b/artfynd/A 15895-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132080747</v>
       </c>
       <c r="B2" t="n">
-        <v>97966</v>
+        <v>97974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132080746</v>
       </c>
       <c r="B3" t="n">
-        <v>97963</v>
+        <v>97971</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15895-2026 artfynd.xlsx
+++ b/artfynd/A 15895-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132080747</v>
       </c>
       <c r="B2" t="n">
-        <v>97974</v>
+        <v>97984</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132080746</v>
       </c>
       <c r="B3" t="n">
-        <v>97971</v>
+        <v>97981</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15895-2026 artfynd.xlsx
+++ b/artfynd/A 15895-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132080747</v>
       </c>
       <c r="B2" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132080746</v>
       </c>
       <c r="B3" t="n">
-        <v>97981</v>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15895-2026 artfynd.xlsx
+++ b/artfynd/A 15895-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132080747</v>
       </c>
       <c r="B2" t="n">
-        <v>97986</v>
+        <v>97987</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132080746</v>
       </c>
       <c r="B3" t="n">
-        <v>97983</v>
+        <v>97984</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15895-2026 artfynd.xlsx
+++ b/artfynd/A 15895-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132080747</v>
       </c>
       <c r="B2" t="n">
-        <v>97987</v>
+        <v>97989</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132080746</v>
       </c>
       <c r="B3" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15895-2026 artfynd.xlsx
+++ b/artfynd/A 15895-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132080747</v>
+        <v>132080746</v>
       </c>
       <c r="B2" t="n">
-        <v>97989</v>
+        <v>98060</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597467</v>
+        <v>597343</v>
       </c>
       <c r="R2" t="n">
-        <v>6680939</v>
+        <v>6680930</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132080746</v>
+        <v>132080747</v>
       </c>
       <c r="B3" t="n">
-        <v>97986</v>
+        <v>98063</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,16 +783,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597343</v>
+        <v>597467</v>
       </c>
       <c r="R3" t="n">
-        <v>6680930</v>
+        <v>6680939</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 15895-2026 artfynd.xlsx
+++ b/artfynd/A 15895-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132080746</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,8 +876,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132080747</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>